--- a/338 Example JMC Rev Mar 2026.xlsx
+++ b/338 Example JMC Rev Mar 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fordhamit-my.sharepoint.com/personal/jcolon_fordham_edu/Documents/Corporate Tax/Corporate Tax Git/Corporate-Tax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B3C9F7D-1AEE-C84A-998E-661F5A6BAD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{7CD24F7D-1016-4246-9B6C-50152E9651E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4780" yWindow="600" windowWidth="46320" windowHeight="25840" xr2:uid="{A22EB111-5571-714F-A8BD-160AC6D4E107}"/>
+    <workbookView xWindow="4880" yWindow="600" windowWidth="46320" windowHeight="25840" xr2:uid="{A22EB111-5571-714F-A8BD-160AC6D4E107}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,16 +166,16 @@
     <t>For no 338(g), would only pay:  (value - unrealized tax liab); for 338(g), would be: value less realized tax liability</t>
   </si>
   <si>
-    <t>In 338(g), tax is borne by purchaser; 1.338-1(b)(3)(3)(i)</t>
-  </si>
-  <si>
-    <t>For (h)(10), stock sale is treated as asset sale by T; Seller bears tax; treated as liquidated aft sale). 1.338(h)(1)-1(d)(3)(i)</t>
-  </si>
-  <si>
     <t>Why 1,000 is gross cost:  ADSP = 811 + 0 Liab +.21(ADSP - 100), = 1000</t>
   </si>
   <si>
     <t>This assumes that all assets qualify under 168(k); if some are intangibles, RP, etc., this number would be smaller</t>
+  </si>
+  <si>
+    <t>In 338(g), tax is borne by purchaser; 1.338-1(b)(3)(i)</t>
+  </si>
+  <si>
+    <t>For (h)(10), stock sale is treated as asset sale by T; Seller bears tax; treated as liquidated aft sale. 1.338(h)(10)-1(d)(3)(i)</t>
   </si>
 </sst>
 </file>
@@ -326,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -362,28 +362,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -781,7 +778,7 @@
         <v>1000</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G8" s="16"/>
     </row>
@@ -818,26 +815,26 @@
     </row>
     <row r="14" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="22"/>
-      <c r="E15" s="23" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="25"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
     </row>
     <row r="16" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D17" s="5" t="s">
@@ -920,7 +917,7 @@
         <v>-189</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
@@ -1114,14 +1111,14 @@
       <c r="G29" s="7">
         <v>811</v>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="7">
         <v>1000</v>
       </c>
       <c r="I29" s="7">
         <v>1000</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1149,7 +1146,7 @@
         <v>-210</v>
       </c>
       <c r="J30" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
